--- a/astro-site/public/dl/kit-tareas-hotel/02-fb-buffet-comida-cena.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/02-fb-buffet-comida-cena.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Buffet Almuerzo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Buffet Cena" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buffet Almuerzo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buffet Cena" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Buffet Almuerzo'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Buffet Cena'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -144,51 +152,62 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -548,15 +567,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -564,6 +584,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -592,9 +613,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -616,8 +635,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -626,18 +662,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -654,6 +690,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -888,6 +925,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1046,6 +1084,7 @@
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -1166,6 +1205,26 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="13" t="n"/>
     </row>
+    <row r="32">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>COUNTIF(E6:E31,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E32">
+        <f>COUNTIF(B6:B31,"?*")</f>
+        <v>22.0</v>
+      </c>
+    </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
@@ -1183,19 +1242,33 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G31">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E28 E29 E30 E31" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E28 E29 E30 E31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1204,18 +1277,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1232,6 +1305,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1428,6 +1502,7 @@
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1566,6 +1641,26 @@
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>COUNTIF(E6:E21,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>COUNTIF(B6:B21,"?*")</f>
+        <v>14.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -1590,11 +1685,25 @@
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G24"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hotel/02-fb-buffet-comida-cena.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/02-fb-buffet-comida-cena.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -637,9 +637,38 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Pescado crudo y vegetales:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ Tartar, ceviche, carpaccio, salmón marinado o ahumado en frío: sólo con congelación previa acreditada (≥ 24 h a −20 °C o 15 h a −35 °C). Es obligación del Reglamento (CE) 853/2004 y en un buffet de autoservicio el riesgo se multiplica por el número de comensales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ Los vegetales que se sirven crudos se desinfectan con lejía apta para uso alimentario a la dosis del fabricante y se ACLARAN con agua potable abundante; los que se blanquean, no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -664,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -760,7 +789,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de ensaladas y fríos: lechuga, tomate, quinoa, pasta fría</t>
+          <t>Montar estación de ensaladas y fríos: lechuga, tomate, quinoa, pasta fría. Los vegetales que se sirven CRUDOS, desinfectados con lejía apta para uso alimentario según la dosis del fabricante (habitual: 70 ppm, 5 min) y ACLARADOS con agua potable abundante</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -798,7 +827,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Montar estación caliente: arroces, pasta, carnes, pescados</t>
+          <t>Carpaccio, salmón y cualquier pescado que se sirva crudo o marinado — prevención de ANISAKIS: exigir al proveedor el certificado de congelación previa (≥ 24 h a −20 °C, o 15 h a −35 °C) o congelarlo tú, y anotar el lote</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -817,7 +846,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de guarniciones: patatas, verduras, legumbres</t>
+          <t>Montar estación caliente: arroces, pasta, carnes, pescados</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -836,7 +865,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Montar show cooking / estación de acción (plancha, wok, pasta)</t>
+          <t>Montar estación de guarniciones: patatas, verduras, legumbres</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -855,7 +884,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de postres: tartas, fruta, helados, lácteos</t>
+          <t>Montar show cooking / estación de acción (plancha, wok, pasta)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -874,7 +903,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Verificar señalización con nombre de plato y alérgenos (14 obligatorios)</t>
+          <t>Montar estación de postres: tartas, fruta, helados, lácteos</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -893,7 +922,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Colocar cubiertos de servicio limpios en cada fuente</t>
+          <t>Verificar señalización con nombre de plato y alérgenos (14 obligatorios)</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -912,7 +941,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperaturas: caliente &gt;65°C, frío &lt;5°C (registrar APPCC)</t>
+          <t>Colocar cubiertos de servicio limpios en cada fuente</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -925,77 +954,77 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Verificar temperaturas antes de abrir: caliente &gt; 65 °C, frío &lt; 5 °C — anota la lectura: ____ °C (si tienes el Pack APPCC, regístrala en su hoja de temperaturas; si no, en la columna «Notas»)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Reposición durante servicio</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Ronda de reposición cada 15-20 min (nunca dejar fuentes vacías)</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Cambiar fuentes completas (no rellenar sobre comida existente)</t>
+          <t>Ronda de reposición cada 15-20 min (nunca dejar fuentes vacías)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -1010,11 +1039,11 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Mantener show cooking activo con chef visible y producto fresco</t>
+          <t>Cambiar fuentes completas (no rellenar sobre comida existente)</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -1029,11 +1058,11 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Reponer bebidas: agua, zumos, refrescos, vino de la casa</t>
+          <t>Mantener show cooking activo con chef visible y producto fresco</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -1048,16 +1077,16 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Limpiar derrames inmediatamente y mantener línea presentable</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Reponer bebidas: agua, zumos, refrescos, vino de la casa</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D23" s="11" t="n"/>
@@ -1067,16 +1096,16 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Registrar reposiciones para ajustar producción (qué se acaba primero)</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Cocina</t>
+          <t>Limpiar derrames inmediatamente y mantener línea presentable</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
         </is>
       </c>
       <c r="D24" s="11" t="n"/>
@@ -1084,82 +1113,82 @@
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Registrar reposiciones para ajustar producción (qué se acaba primero)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Cierre del buffet</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Retirar estaciones gradualmente (señalización primero)</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Registrar sobrantes por estación para control de mermas</t>
+          <t>Retirar estaciones gradualmente (señalización primero)</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Cocina</t>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D29" s="11" t="n"/>
@@ -1169,16 +1198,16 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Desmontar chafing dishes, limpiar y almacenar</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Registrar sobrantes por estación para control de mermas</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D30" s="11" t="n"/>
@@ -1188,11 +1217,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Limpiar línea de buffet, suelos y mesas de apoyo</t>
+          <t>Desmontar chafing dishes, limpiar y almacenar</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -1206,34 +1235,53 @@
       <c r="G31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="17" t="inlineStr">
+      <c r="A32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Limpiar línea de buffet, suelos y mesas de apoyo</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C32">
-        <f>COUNTIF(E6:E31,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33">
+        <f>COUNTIFS(B6:B32,"?*",E6:E32,"✓")-COUNTIFS(B6:B32,"Tarea",E6:E32,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E32">
-        <f>COUNTIF(B6:B31,"?*")</f>
-        <v>22.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E33">
+        <f>COUNTIF(B6:B32,"?*")-COUNTIF(B6:B32,"Tarea")-COUNTIF(E6:E32,"N/A")</f>
+        <v>21.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1242,21 +1290,21 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A35:G35"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G31">
+  <conditionalFormatting sqref="A6:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E28 E29 E30 E31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1279,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1394,7 +1442,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Montar estación caliente: platos de cena (más elaborados que almuerzo)</t>
+          <t>Tartar, ceviche y pescado crudo de la estación premium — prevención de ANISAKIS: sólo pescado con congelación previa acreditada (≥ 24 h a −20 °C, o 15 h a −35 °C); anota el lote y no lo montes hasta el momento del servicio</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1413,7 +1461,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Montar show cooking especial de cena: parrilla, robata, flambé</t>
+          <t>Montar estación caliente: platos de cena (más elaborados que almuerzo)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1432,7 +1480,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de quesos con selección de vinos</t>
+          <t>Montar show cooking especial de cena: parrilla, robata, flambé</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1451,7 +1499,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de postres elaborados y petit fours</t>
+          <t>Montar estación de quesos con selección de vinos</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -1470,12 +1518,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Verificar carta de vinos disponible en sala (servicio a mesa)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Sala</t>
+          <t>Montar estación de postres elaborados y petit fours</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D12" s="11" t="n"/>
@@ -1489,7 +1537,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Colocar velas o iluminación decorativa según estándar</t>
+          <t>Verificar carta de vinos disponible en sala (servicio a mesa)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1502,82 +1550,82 @@
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Colocar velas o iluminación decorativa según estándar</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Servicio y cierre</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Reposición igual que almuerzo: cada 15-20 min, fuentes completas</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Coordinar con bar del hotel para servicio de cócteles pre-cena</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sala</t>
+          <t>Reposición igual que almuerzo: cada 15-20 min, fuentes completas</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -1587,11 +1635,11 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Ofrecer café, infusiones y digestivos al finalizar</t>
+          <t>Coordinar con bar del hotel para servicio de cócteles pre-cena</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1606,16 +1654,16 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Cierre y desmontaje siguiendo mismo protocolo que almuerzo</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Buffet</t>
+          <t>Ofrecer café, infusiones y digestivos al finalizar</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Sala</t>
         </is>
       </c>
       <c r="D20" s="11" t="n"/>
@@ -1625,16 +1673,16 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Preparar mise en place del desayuno siguiente si hay turno cruzado</t>
+          <t>Cierre y desmontaje siguiendo mismo protocolo que almuerzo</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Cocina</t>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D21" s="11" t="n"/>
@@ -1643,34 +1691,53 @@
       <c r="G21" s="13" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="A22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Preparar mise en place del desayuno siguiente si hay turno cruzado</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C22">
-        <f>COUNTIF(E6:E21,"✓")</f>
-        <v>1.0</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23">
+        <f>COUNTIFS(B6:B22,"?*",E6:E22,"✓")-COUNTIFS(B6:B22,"Tarea",E6:E22,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E22">
-        <f>COUNTIF(B6:B21,"?*")</f>
+      <c r="E23">
+        <f>COUNTIF(B6:B22,"?*")-COUNTIF(B6:B22,"Tarea")-COUNTIF(E6:E22,"N/A")</f>
         <v>14.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1679,20 +1746,20 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G21">
+  <conditionalFormatting sqref="A6:G22">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E18 E19 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-hotel/02-fb-buffet-comida-cena.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/02-fb-buffet-comida-cena.xlsx
@@ -1292,9 +1292,9 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A35:G35"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G32">
@@ -1749,8 +1749,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G22">
     <cfRule type="expression" priority="1" dxfId="0">
